--- a/光伏配储项目/电价数据/2026/临港站.xlsx
+++ b/光伏配储项目/电价数据/2026/临港站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.55423</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.73389</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1.17774</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.19552</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.23089</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.24288</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1.17265</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1.17293</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.7291599999999999</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.7821399999999999</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.71475</v>
+      </c>
+      <c r="N117" t="n">
+        <v>1.17174</v>
+      </c>
+      <c r="O117" t="n">
+        <v>1.17164</v>
+      </c>
+      <c r="P117" t="n">
+        <v>1.17151</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.70804</v>
+      </c>
+      <c r="R117" t="n">
+        <v>1.17232</v>
+      </c>
+      <c r="S117" t="n">
+        <v>1.17203</v>
+      </c>
+      <c r="T117" t="n">
+        <v>1.17092</v>
+      </c>
+      <c r="U117" t="n">
+        <v>1.17169</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.76249</v>
+      </c>
+      <c r="W117" t="n">
+        <v>1.17212</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39494</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>1.17206</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>1.17617</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.78047</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>1.20058</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>1.28151</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.40479</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.8875700000000001</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.69552</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.6899</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.47069</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.7578400000000001</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.78104</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.40421</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.39344</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.04966</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1.03882</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.13048</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.76036</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.72288</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.50863</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.41068</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.40699</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.41128</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.79298</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.98613</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.34864</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.5311399999999999</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.78504</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.43011</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.7932899999999999</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.7664099999999999</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.9618099999999999</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.92574</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.07716</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.35348</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.20792</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.24602</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.74886</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.25479</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.19681</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.10624</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.25613</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.55026</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.26653</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.28374</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.50024</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.3407</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.25977</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.44007</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.3806</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.31279</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.81794</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47924</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.41065</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4219</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.19234</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.04613</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.18284</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53623</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51624</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.8047000000000001</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.70689</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.7790199999999999</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.68551</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.6770900000000001</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.79792</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.74226</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.74279</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.74275</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.74246</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.72419</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.7864800000000001</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.09121</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.45135</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.03044</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.78298</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.67659</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.74227</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.64436</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.96193</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.17489</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.8001900000000001</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.13138</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.06034</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1.02258</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.72724</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.55572</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.57851</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.6987599999999999</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.20002</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.2657</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.51558</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.19567</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.6696</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.09258</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.8457</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.27892</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.16968</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.29702</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.6261599999999999</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.65267</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.5760599999999999</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.6273</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.21063</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.20286</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.21049</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.20366</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.00167</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.1837</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.1988</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.19535</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.67588</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.19806</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20791</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.26419</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.56217</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.47807</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.20327</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.50647</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.26638</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.75625</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.76385</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.91412</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44059</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41382</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.74771</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.94096</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.89473</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.6490199999999999</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.7454299999999999</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.64612</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.56694</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.93947</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.9305399999999999</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.88119</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.76264</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.94077</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.7386900000000001</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.93902</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.6452599999999999</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.7446900000000001</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.6463300000000001</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.74429</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.7410599999999999</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.7031499999999999</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.74095</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.74064</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.65291</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.7078300000000001</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.83973</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.12016</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.88181</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.7671699999999999</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.71424</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.60948</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.64147</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.42644</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.7457</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.18447</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.56125</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.69686</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.19316</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.67167</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.19581</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.19939</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.8090700000000001</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.97454</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.20121</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.20129</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.90832</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5632999999999999</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.41469</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47715</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.67986</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.18879</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.05341</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.19973</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.44053</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.28278</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.19877</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.22344</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.21445</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.44837</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.29292</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.30794</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.66999</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.21634</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.21431</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.07079</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.10333</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.1242</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.11027</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.2394</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.19532</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.2827</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>1.02397</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.7700399999999999</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.72741</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.53865</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41307</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34314</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.19312</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.9264</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.90996</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.8816000000000001</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1.05101</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.7331</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.8906000000000001</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.76162</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.9660700000000001</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.9378200000000001</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.87346</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.74214</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.74218</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.53576</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.6410399999999999</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.5455099999999999</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.52876</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.7611599999999999</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.74237</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.89003</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.74091</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.68635</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.64407</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.54923</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.68728</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.7244700000000001</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.94216</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.19616</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.33949</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.86297</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.58183</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.67243</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.91312</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.89455</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.18984</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.44737</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.77919</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.98765</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.24814</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.70957</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.11823</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.53052</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.49268</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.67004</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.02585</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.12737</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.26599</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.19937</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.1003</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1.01559</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.03518</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.99913</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.29623</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.4773</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.8143400000000001</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.38269</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.23404</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.86598</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.10663</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.18665</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.13425</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.18935</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.28604</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.34645</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.18919</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.2999</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.19184</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.1861</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.21645</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.22833</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.21402</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.19108</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.18983</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.74287</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.53164</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.74699</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32199</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.75001</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.49967</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40627</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.48464</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.51118</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.53049</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.40585</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.46471</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.43332</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.46268</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.7284299999999999</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.86181</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.62518</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.71339</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.73882</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.85936</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.71696</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.56009</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.55914</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.54772</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.6023999999999999</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47878</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.10196</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.28603</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.5561499999999999</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.4919</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.5234</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.46907</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.64981</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.51232</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.4919</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.40316</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.49233</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.4956</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.60853</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.40636</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.5133799999999999</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.51234</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40945</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.49144</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.41095</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40545</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3443</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.21897</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.01173</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.5993200000000001</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.79226</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.79311</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.72281</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.79269</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.79312</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.79292</v>
+      </c>
+      <c r="N122" t="n">
+        <v>1.17159</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.79286</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.79274</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.79287</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.7934099999999999</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.79343</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.27829</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07492</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04281</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04375</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.04663</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.27509</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.08404</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.29667</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.13118</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04452</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.0466</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04649</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0.00359</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04627000000000001</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04507</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04618</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04546</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.26866</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.28595</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.29396</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.39305</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.43022</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36597</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.44861</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.79223</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.79271</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.79275</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.79332</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.79314</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39773</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33457</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.76395</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.69397</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.27865</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.29119</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28743</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27492</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.76459</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.90151</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.69384</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.66791</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.68551</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.76818</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.96658</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.41253</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.48408</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.7464299999999999</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.7493500000000001</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.9131699999999999</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.69817</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.54795</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.48515</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.45679</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.09411</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.74515</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.75038</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.65471</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.61424</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48068</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.73995</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79101</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.79103</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.61075</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.7543500000000001</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.03081</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.43131</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.86115</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.46091</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.34754</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.81216</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.40635</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.06509</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.42671</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.788</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.46535</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.78716</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80103</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303600000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78769</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78555</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87914</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50258</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41214</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46078</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21925</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6393799999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5414099999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.80752</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.79253</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.7927000000000001</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.7924</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.79287</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.6989</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.79299</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.79296</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.66031</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.64535</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.67161</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38636</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.79322</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.79414</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.7900700000000001</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.78974</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.79138</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.79232</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.79149</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.75721</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.66227</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.7925399999999999</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.64538</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.6002000000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43741</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5648</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66699</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07801</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.64746</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.50905</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.57692</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59681</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.00952</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.34247</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.31105</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.27308</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.5611499999999999</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.80025</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.57651</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.65644</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.55841</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.9893</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.78734</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.7360399999999999</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.6513300000000001</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.58353</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>1.02168</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>1.15439</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.5700299999999999</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.7548899999999999</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.74679</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.79332</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.6987300000000001</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.7484700000000001</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.89442</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.7468899999999999</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.74759</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.60994</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.59201</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.74839</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.7942899999999999</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.79325</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.7944099999999999</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.7918500000000001</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.78464</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.79274</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.80149</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.79253</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.79918</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.79691</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.7923600000000001</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.7922899999999999</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.79274</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.7926599999999999</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.79299</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.7935599999999999</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.80392</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.79306</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.79286</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.7930499999999999</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.79316</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.79325</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.65964</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95612</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.74476</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.9426100000000001</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.89116</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.94432</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.77634</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.77861</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.6952699999999999</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.7440099999999999</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37523</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.64534</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.66428</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.41123</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.53303</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.63001</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.75038</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.90035</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.15333</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.94163</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.56062</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.12579</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.8681</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.9765199999999999</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.8855299999999999</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.65416</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.8354299999999999</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.0973</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.74218</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.53411</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.43811</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.90411</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>1.21172</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.94223</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.23621</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.8078</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.8389800000000001</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.94392</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.7606000000000001</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40838</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37644</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47805</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39567</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.38147</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.44487</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.38334</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39764</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.50059</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.42045</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41591</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.20056</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51797</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79534</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64979</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.80349</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.43918</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.77019</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.19075</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.93489</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.6579700000000001</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.7153400000000001</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.57842</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.1775</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.63538</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.9227300000000001</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.59981</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.78932</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.54018</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.46359</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.43159</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.7922</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.21288</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.54203</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.6164500000000001</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.87249</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.52896</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.76414</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.0967</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.0955</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.96178</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.99627</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.9501499999999999</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.18685</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.18507</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.88878</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.18511</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.63112</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.99752</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.04146</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.18512</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.9779500000000001</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.01887</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.60813</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.95043</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>1.00733</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.11456</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.9118200000000001</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.8994500000000001</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.12436</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.61288</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.98624</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>1.02359</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.75849</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38619</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36888</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.34323</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.89075</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.74165</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.74195</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.6978300000000001</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.59524</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.7208600000000001</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.39408</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.94665</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.7506</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.69992</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.74636</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.69786</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.74748</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.8357599999999999</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.72712</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.8934</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.76359</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>1.15736</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>1.45751</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.7656799999999999</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.76789</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.7696499999999999</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.70552</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.7085199999999999</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.7690399999999999</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.89895</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.90551</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.76564</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.6474</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.64103</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.65081</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.6531</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37221</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.69941</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40323</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.4054</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.69517</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.69411</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45673</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.6940599999999999</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.69685</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.61077</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.54677</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.59614</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.89006</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.7920199999999999</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.79227</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.7918200000000001</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.81096</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.69397</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.73834</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.59539</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.49716</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.59534</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.49716</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.76297</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.80153</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.7920199999999999</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.76275</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.6936</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.69316</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.6465599999999999</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.55859</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.29407</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.28219</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26677</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.4733</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.4871</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.7054</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.60581</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.6266</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.84709</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.26798</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.16331</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.8503099999999999</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39629</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42854</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.7001900000000001</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.93811</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.16502</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.11897</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.01569</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.5412100000000001</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.43858</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42936</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39696</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49693</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44722</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42592</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.5658099999999999</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.64298</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.64009</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.6429900000000001</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.59765</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.76423</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.49985</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.5976</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.49875</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.5969800000000001</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.6664099999999999</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.76376</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.68948</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.7626499999999999</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>1.12827</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.47052</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.41498</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.30447</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>1.00114</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.98986</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.9914299999999999</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56144</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.55213</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.94387</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.08364</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.79165</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.01065</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.77567</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.65621</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.64895</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.71625</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.7969299999999999</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.29463</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.76962</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.35752</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.49394</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.16554</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.99287</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.65855</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.63165</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.66528</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.67865</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.67372</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.6507</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.67519</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20675</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.70813</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.78991</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.70542</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.7132</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.72135</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.64026</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.75564</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.01906</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.12846</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.69926</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.70769</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.70147</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.78109</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.73125</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.8204</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.67176</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.26721</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.64786</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.7628400000000001</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.6383099999999999</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.67171</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34485</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.6327200000000001</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.78301</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.36873</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.6585599999999999</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.7638400000000001</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.6724</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.64508</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.8005800000000001</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.76464</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.7649600000000001</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.66322</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.62403</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40264</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42692</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.7536900000000001</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49542</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.5136000000000001</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.5220900000000001</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28471</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.4079700000000001</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45343</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.9298</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.48305</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.18941</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.90024</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.76162</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.44963</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39421</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.4572</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50008</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.50015</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.45074</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.49167</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39307</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.38941</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40589</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40591</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30054</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.62194</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.41939</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.38826</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.45067</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.7532799999999999</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.4279</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.5180499999999999</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.70183</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49855</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.40687</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.42014</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42849</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42288</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5660499999999999</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42649</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45523</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40159</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.66939</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.45031</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.45184</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43036</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65181</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83158</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47208</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.7045399999999999</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.66959</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.66467</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1.25597</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.6529700000000001</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.57345</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.53311</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.46055</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.48889</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.45788</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.43883</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.51575</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.41831</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.54457</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.75983</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.7663300000000001</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27858</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.48293</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39384</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.54412</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.5008899999999999</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.71999</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.76054</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.55296</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50101</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.01797</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.48226</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.44286</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.09127</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.12693</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.08005</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.11069</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.12733</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.01727</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.19302</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.1413</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.13023</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.17566</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.8418300000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.19053</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.84805</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.34006</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.90134</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.70806</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.75591</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.9469299999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.5869</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.7237100000000001</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.71266</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.7929400000000001</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.61212</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.7600800000000001</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.41251</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.74388</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42772</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.69868</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.94467</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.93362</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.71147</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.69379</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.86814</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.88391</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.89035</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.71745</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.9116599999999999</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.71554</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.88236</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.6483300000000001</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.5782200000000001</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.58211</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.5820599999999999</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.65013</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.47814</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.57823</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.4693</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.76389</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.62438</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.5784</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.8746799999999999</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.65747</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.10959</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.79859</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.7614</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.2996</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.36009</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.74248</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.66449</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.36855</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1.00481</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.61075</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.50068</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.50093</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.54861</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.6001599999999999</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.75129</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.20081</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.7057100000000001</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.9383899999999999</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.68055</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.96016</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.90442</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.76373</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.73342</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.18547</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.18665</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.44996</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.26362</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.66428</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.24802</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.29347</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.11236</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.43555</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.04142</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.97345</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.90743</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.44841</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.34342</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.6977000000000001</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.49813</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.58092</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.47643</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44964</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48768</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40529</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.5319400000000001</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.53476</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.79906</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.6839700000000001</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.66637</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.50382</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.08541</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.69133</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.66531</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.80237</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.08133</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.19405</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.50017</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.19858</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.54672</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.15904</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5574199999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.5708099999999999</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42749</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.5018899999999999</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23502</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37363</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42947</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.48241</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.4629</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.50686</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.51097</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46035</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41266</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43326</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.54315</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.52113</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.60682</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.76106</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.13913</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.8735000000000001</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.76351</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.5117200000000001</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.44536</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.41989</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34298</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.42008</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.42073</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.43632</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.38372</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.5007699999999999</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.46289</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.45008</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44643</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.5904700000000001</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.48389</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.44982</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46385</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.45062</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.46493</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.55399</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.3928</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.45005</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42535</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39847</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41263</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.46137</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.42029</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46925</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.6962</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.65888</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.66359</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.64325</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.49855</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.44881</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.39927</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1.04931</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.49685</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.69565</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.4982200000000001</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.49854</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.6248400000000001</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.6185</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.61342</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.6131</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.2346</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30764</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.27309</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.38876</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38838</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.15398</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.73758</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.21526</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.38761</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.30158</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.27324</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.14087</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.39906</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.69968</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.5681</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.49993</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.76379</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39282</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38314</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37218</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38303</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.44892</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.44954</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.44941</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.39319</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39331</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38268</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42904</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.80874</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.46813</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39331</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38936</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40278</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.37109</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.49071</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.10332</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.38589</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.19198</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1.08249</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.5261</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.7610800000000001</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.7608200000000001</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.51551</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41792</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.42961</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42731</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.4094</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41651</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39602</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38829</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44544</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.55964</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.4276</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.44506</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.69331</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1.29102</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42608</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.76432</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.80436</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45535</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40367</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.7605700000000001</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.41258</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52959</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.47701</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.48036</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.24415</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.0885</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.98693</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.31719</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.63652</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.55187</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38908</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49799</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.5838300000000001</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.7611</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.55098</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.5496</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39688</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.23664</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.76474</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.76201</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.45287</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.49848</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>1.01363</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.7725</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.62838</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.7611599999999999</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.20489</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.60895</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.75124</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.63958</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.26827</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.9017000000000001</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.88603</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.90651</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.9250900000000001</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.17686</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.65115</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.95985</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.69478</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.98577</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.65949</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.6783</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.76019</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.65996</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.26461</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.04504</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.02597</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.03514</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.54894</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.36514</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.05887</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.41069</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38158</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.76034</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.39002</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34554</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.55983</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.80776</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.55288</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.75712</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.7589400000000001</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.5624600000000001</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.4709</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.4604</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40812</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42954</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.4202</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.38698</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38383</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.42327</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40585</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42778</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.6386000000000001</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.59601</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.5641</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.54308</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.45275</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.48184</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.50025</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.5605399999999999</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.81375</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.17773</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.13356</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.04646</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.13629</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.75011</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.74486</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.0573</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.07566</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.68403</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.55459</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.56102</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.5612</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.48006</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2885</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.48451</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.55001</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.55055</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.5469700000000001</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.6622</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.55629</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.05249</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.66318</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.5502100000000001</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.5001</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.50034</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48301</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.50019</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48264</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.50042</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.57852</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.55816</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.5619</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49846</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.51437</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40355</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42359</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.5008899999999999</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.5619</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.66198</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.17581</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.07929</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.66261</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.58392</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.1656</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.8714700000000001</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.66215</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.16378</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.83823</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.49726</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.5122100000000001</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.4996</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.43999</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.5355599999999999</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39952</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34454</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1.0572</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.76419</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.7718700000000001</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1.19108</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.7634099999999999</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.49938</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.41966</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.42017</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.41981</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35316</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38748</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.63014</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.59001</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.42733</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.6426499999999999</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.03167</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.21666</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.93421</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.9869600000000001</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.03447</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.9776699999999999</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.9450499999999999</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.97565</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.9585199999999999</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.94317</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.94565</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.47826</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.8604299999999999</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.23419</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.76112</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.23017</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.31555</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.29741</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.7284400000000001</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.94862</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.86874</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.9357000000000001</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.54956</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.15548</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.71369</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.69213</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.56496</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.27637</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.71166</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.67549</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.7689900000000001</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.8843799999999999</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.58809</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.58982</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.39478</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.70709</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42434</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.69047</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.5482</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.69274</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.74148</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.70048</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3687</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36464</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.4037</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.71066</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46572</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.75015</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.52439</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.51089</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.44379</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.02527</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.9229700000000001</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.03533</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.93326</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.04316</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1.02599</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1.02617</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.38374</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.09614</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.30961</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.6666</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.38893</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.68138</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.62502</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.7374700000000001</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.7225199999999999</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.02301</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.72287</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.7759</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.14956</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.43679</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.65099</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.41811</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.58289</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>1.17766</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.59924</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.64114</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.64295</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.81309</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.7688400000000001</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.80855</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.81114</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37511</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.49788</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38843</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.76039</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43977</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.43843</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37951</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.50005</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.7741</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.4657</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.42204</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.50044</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.62826</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.21374</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.21499</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.14775</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.5262100000000001</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.70099</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09276</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.50151</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.44921</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.43606</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.43568</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.43183</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.50281</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06661</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.5892500000000001</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.04808</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.05869</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.18263</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.62573</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.4301</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.20151</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.29764</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.63175</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.48147</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.11749</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.09811</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.65551</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.17183</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.34082</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.00967</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.77447</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.7719400000000001</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.53824</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.52949</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.48126</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.5192899999999999</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.54228</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39872</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.49157</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.4916</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.52134</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.54212</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.52137</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39324</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.53196</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.52124</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.5213</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.5212599999999999</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.5212599999999999</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.51168</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.49677</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.49674</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.4918</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.49161</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3723399999999999</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84801</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.50092</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37416</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.49778</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.50064</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.5013</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.50038</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.54165</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.54508</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.42556</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.4166</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.6374500000000001</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.79095</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.9349700000000001</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.92208</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.92057</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.03333</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.73129</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.50531</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.46298</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.20071</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.16429</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.9658</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.70847</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.23967</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.47851</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.48354</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.50263</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.47659</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.47313</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.51489</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.55741</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.5439299999999999</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.61341</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.6539299999999999</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.66402</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41774</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.52585</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.54098</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.5482400000000001</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.62485</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.59039</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.56467</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.6711</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.59166</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.57594</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.65759</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.6160399999999999</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.61281</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.6159199999999999</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.85017</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.5944700000000001</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.5900599999999999</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.6701</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.57317</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.63734</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.58728</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.56047</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.5578099999999999</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.54113</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.6952</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.6077400000000001</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.60825</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.53173</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.53179</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.5325700000000001</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51535</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.55376</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.5210399999999999</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.5011100000000001</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45963</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45987</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43855</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39903</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41204</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49492</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.54738</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.5198200000000001</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.52012</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.52177</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.5300499999999999</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.36059</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.66496</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.50818</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.52181</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.52989</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.52866</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.5231</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.5297500000000001</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.50445</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.5213099999999999</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.54552</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.5489299999999999</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.5161399999999999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.52075</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.61466</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.5208200000000001</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.52195</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.52151</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.5277500000000001</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.52127</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.52727</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.5283099999999999</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.53723</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.52683</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.52483</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.5691799999999999</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.53779</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.54253</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.5561200000000001</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.55868</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.5305599999999999</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.53323</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.5463300000000001</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.40144</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.73346</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.83311</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.8165</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.6215900000000001</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.81536</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.7644</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.63825</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.62571</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.60895</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.65004</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.6459</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.62024</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.61612</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.71916</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.6782699999999999</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.82747</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.70382</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.60798</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.53089</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.5123799999999999</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
